--- a/TCS vs Infosys - Financial Analysis.xlsx
+++ b/TCS vs Infosys - Financial Analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ef8dac754791c639/Documents/Projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1661" documentId="13_ncr:1_{D5F36114-F850-4553-AFA4-5880D5F76738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{005DBA00-D568-4F7F-A3A3-B5AB03C79CF5}"/>
+  <xr:revisionPtr revIDLastSave="1706" documentId="13_ncr:1_{D5F36114-F850-4553-AFA4-5880D5F76738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{048481D6-15F9-4BB1-A05E-64F3C5BA578F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{D24AA4B4-05AD-4E77-90C6-9BD8BC46B51E}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="81">
   <si>
     <t>FY23</t>
   </si>
@@ -505,6 +505,9 @@
   </si>
   <si>
     <t>Strength- TCS &amp; Infosys</t>
+  </si>
+  <si>
+    <t>Operating Profit Margin%</t>
   </si>
 </sst>
 </file>
@@ -984,7 +987,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1129,6 +1132,27 @@
     <xf numFmtId="0" fontId="28" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1160,26 +1184,8 @@
     <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="9" fontId="9" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -9602,11 +9608,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DDB5D37-2412-4859-8405-D298984CB7F6}">
-  <dimension ref="B1:S29"/>
+  <dimension ref="B1:S31"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" style="2" customWidth="1"/>
-    <col min="2" max="2" width="24" style="2" customWidth="1"/>
+    <col min="2" max="2" width="34.44140625" style="2" customWidth="1"/>
     <col min="3" max="3" width="2" style="2" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="10.6640625" style="2" customWidth="1"/>
     <col min="5" max="6" width="10.44140625" style="2" bestFit="1" customWidth="1"/>
@@ -9633,17 +9639,17 @@
         <v>34</v>
       </c>
       <c r="C3" s="10"/>
-      <c r="D3" s="78" t="s">
+      <c r="D3" s="67" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
       <c r="G3" s="10"/>
-      <c r="H3" s="78" t="s">
+      <c r="H3" s="67" t="s">
         <v>36</v>
       </c>
-      <c r="I3" s="78"/>
-      <c r="J3" s="78"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="67"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="10"/>
@@ -9683,417 +9689,479 @@
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="15" t="s">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="C6" s="15"/>
       <c r="D6" s="18">
+        <f>'TCS Data'!C6/'TCS Data'!C4</f>
+        <v>0.26283831134845514</v>
+      </c>
+      <c r="E6" s="18">
+        <f>'TCS Data'!D6/'TCS Data'!D4</f>
+        <v>0.26690688396923118</v>
+      </c>
+      <c r="F6" s="18">
+        <f>'TCS Data'!E6/'TCS Data'!E4</f>
+        <v>0.26400573389105608</v>
+      </c>
+      <c r="G6" s="84"/>
+      <c r="H6" s="18">
+        <f>'Infosys Data'!C6/'Infosys Data'!C4</f>
+        <v>0.23935898396778568</v>
+      </c>
+      <c r="I6" s="18">
+        <f>'Infosys Data'!D6/'Infosys Data'!D4</f>
+        <v>0.23703390381987374</v>
+      </c>
+      <c r="J6" s="18">
+        <f>'Infosys Data'!E6/'Infosys Data'!E4</f>
+        <v>0.24072642493404503</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="15"/>
+      <c r="D7" s="18">
         <f>'TCS Data'!C7/'TCS Data'!C4</f>
         <v>0.18693947431450647</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E7" s="18">
         <f>'TCS Data'!D7/'TCS Data'!D4</f>
         <v>0.19057423835478823</v>
       </c>
-      <c r="F6" s="18">
+      <c r="F7" s="18">
         <f>'TCS Data'!E7/'TCS Data'!E4</f>
         <v>0.1901623035828986</v>
       </c>
-      <c r="G6" s="19"/>
-      <c r="H6" s="18">
+      <c r="G7" s="19"/>
+      <c r="H7" s="18">
         <f>'Infosys Data'!C7/'Infosys Data'!C4</f>
         <v>0.16417178248516356</v>
       </c>
-      <c r="I6" s="18">
+      <c r="I7" s="18">
         <f>'Infosys Data'!D7/'Infosys Data'!D4</f>
         <v>0.17070996290752913</v>
       </c>
-      <c r="J6" s="18">
+      <c r="J7" s="18">
         <f>'Infosys Data'!E7/'Infosys Data'!E4</f>
         <v>0.16389349039818393</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B7" s="15" t="s">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B8" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="15"/>
-      <c r="D7" s="18">
+      <c r="C8" s="15"/>
+      <c r="D8" s="18">
         <f>'TCS Data'!C7/'TCS Data'!C13</f>
         <v>0.46610413164646552</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E8" s="18">
         <f>'TCS Data'!D7/'TCS Data'!D13</f>
         <v>0.50733238294157301</v>
       </c>
-      <c r="F7" s="18">
+      <c r="F8" s="18">
         <f>'TCS Data'!E7/'TCS Data'!E13</f>
         <v>0.51240027016758838</v>
       </c>
-      <c r="G7" s="19"/>
-      <c r="H7" s="18">
+      <c r="G8" s="19"/>
+      <c r="H8" s="18">
         <f>'Infosys Data'!C7/'Infosys Data'!C13</f>
         <v>0.31953266938082669</v>
       </c>
-      <c r="I7" s="18">
+      <c r="I8" s="18">
         <f>'Infosys Data'!D7/'Infosys Data'!D13</f>
         <v>0.29770983703300197</v>
       </c>
-      <c r="J7" s="18">
+      <c r="J8" s="18">
         <f>'Infosys Data'!E7/'Infosys Data'!E13</f>
         <v>0.27878895405873633</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="15" t="s">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="15"/>
-      <c r="D8" s="18">
+      <c r="C9" s="15"/>
+      <c r="D9" s="18">
         <f>'TCS Data'!C7/'TCS Data'!C12</f>
         <v>0.29502516467285927</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E9" s="18">
         <f>'TCS Data'!D7/'TCS Data'!D12</f>
         <v>0.31557963044434667</v>
       </c>
-      <c r="F8" s="18">
+      <c r="F9" s="18">
         <f>'TCS Data'!E7/'TCS Data'!E12</f>
         <v>0.30604037844549919</v>
       </c>
-      <c r="G8" s="19"/>
-      <c r="H8" s="18">
+      <c r="G9" s="19"/>
+      <c r="H9" s="18">
         <f>'Infosys Data'!C7/'Infosys Data'!C12</f>
         <v>0.19338502038588717</v>
       </c>
-      <c r="I8" s="18">
+      <c r="I9" s="18">
         <f>'Infosys Data'!D7/'Infosys Data'!D12</f>
         <v>0.19097990681421084</v>
       </c>
-      <c r="J8" s="18">
+      <c r="J9" s="18">
         <f>'Infosys Data'!E7/'Infosys Data'!E12</f>
         <v>0.18074359755066138</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B9" s="15" t="s">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="15"/>
+      <c r="D10" s="18">
+        <f>'TCS Data'!C21</f>
+        <v>0.59144200257344837</v>
+      </c>
+      <c r="E10" s="18">
+        <f>'TCS Data'!D21</f>
+        <v>0.63853485367863205</v>
+      </c>
+      <c r="F10" s="18">
+        <f>'TCS Data'!E21</f>
+        <v>0.65259698605532468</v>
+      </c>
+      <c r="G10" s="19"/>
+      <c r="H10" s="18">
+        <f>'Infosys Data'!C21</f>
+        <v>0.40850908648878625</v>
+      </c>
+      <c r="I10" s="18">
+        <f>'Infosys Data'!D21</f>
+        <v>0.40468195869708795</v>
+      </c>
+      <c r="J10" s="18">
+        <f>'Infosys Data'!E21</f>
+        <v>0.37925393975663274</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="15"/>
-      <c r="D9" s="18">
+      <c r="C11" s="15"/>
+      <c r="D11" s="18">
         <f>('TCS Data'!C6+'TCS Data'!C10)/'TCS Data'!C4</f>
         <v>0.28511297004320096</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E11" s="18">
         <f>('TCS Data'!D6+'TCS Data'!D10)/'TCS Data'!D4</f>
         <v>0.28760071899141942</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F11" s="18">
         <f>('TCS Data'!E6+'TCS Data'!E10)/'TCS Data'!E4</f>
         <v>0.28453651047296769</v>
       </c>
-      <c r="G9" s="19"/>
-      <c r="H9" s="18">
+      <c r="G11" s="19"/>
+      <c r="H11" s="18">
         <f>('Infosys Data'!C6+'Infosys Data'!C10)/'Infosys Data'!C4</f>
         <v>0.26814610913897541</v>
       </c>
-      <c r="I9" s="18">
+      <c r="I11" s="18">
         <f>('Infosys Data'!D6+'Infosys Data'!D10)/'Infosys Data'!D4</f>
         <v>0.26747575974490789</v>
       </c>
-      <c r="J9" s="18">
+      <c r="J11" s="18">
         <f>('Infosys Data'!E6+'Infosys Data'!E10)/'Infosys Data'!E4</f>
         <v>0.270249708571078</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B11" s="14" t="s">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="15"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B12" s="15" t="s">
+      <c r="C13" s="15"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="15"/>
-      <c r="D12" s="20">
+      <c r="C14" s="15"/>
+      <c r="D14" s="20">
         <f>('TCS Data'!C15)/'TCS Data'!C16</f>
         <v>1.876036382327307</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E14" s="20">
         <f>'TCS Data'!D15/'TCS Data'!D16</f>
         <v>1.9705719517908096</v>
       </c>
-      <c r="F12" s="20">
+      <c r="F14" s="20">
         <f>'TCS Data'!E15/'TCS Data'!E16</f>
         <v>1.8914515329993946</v>
       </c>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20">
+      <c r="G14" s="20"/>
+      <c r="H14" s="20">
         <f>'Infosys Data'!C15/'Infosys Data'!C16</f>
         <v>1.8489850819271216</v>
       </c>
-      <c r="I12" s="20">
+      <c r="I14" s="20">
         <f>'Infosys Data'!D15/'Infosys Data'!D16</f>
         <v>2.0746484040601687</v>
       </c>
-      <c r="J12" s="20">
+      <c r="J14" s="20">
         <f>'Infosys Data'!E15/'Infosys Data'!E16</f>
         <v>2.1138057142857143</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B13" s="15" t="s">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B15" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="20">
+      <c r="C15" s="15"/>
+      <c r="D15" s="20">
         <f>('TCS Data'!C15-'TCS Data'!C17)/'TCS Data'!C16</f>
         <v>1.8754106420542158</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E15" s="20">
         <f>('TCS Data'!D15-'TCS Data'!D17)/'TCS Data'!D16</f>
         <v>1.9699757250542993</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F15" s="20">
         <f>('TCS Data'!E15-'TCS Data'!E17)/'TCS Data'!E16</f>
         <v>1.8910662189684593</v>
       </c>
-      <c r="G13" s="20"/>
-      <c r="H13" s="20">
+      <c r="G15" s="20"/>
+      <c r="H15" s="20">
         <f>('Infosys Data'!C15-'Infosys Data'!C17)/'Infosys Data'!C16</f>
         <v>1.8489850819271216</v>
       </c>
-      <c r="I13" s="20">
+      <c r="I15" s="20">
         <f>('Infosys Data'!D15-'Infosys Data'!D17)/'Infosys Data'!D16</f>
         <v>2.0746484040601687</v>
       </c>
-      <c r="J13" s="20">
+      <c r="J15" s="20">
         <f>('Infosys Data'!E15-'Infosys Data'!E17)/'Infosys Data'!E16</f>
         <v>2.1138057142857143</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B15" s="14" t="s">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+    </row>
+    <row r="17" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B17" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B16" s="15" t="s">
+      <c r="C17" s="15"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+    </row>
+    <row r="18" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B18" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="20">
+      <c r="C18" s="15"/>
+      <c r="D18" s="20">
         <f>'TCS Data'!C4/'TCS Data'!C12</f>
         <v>1.5781854835887132</v>
       </c>
-      <c r="E16" s="20">
+      <c r="E18" s="20">
         <f>'TCS Data'!D4/'TCS Data'!D12</f>
         <v>1.6559406621205455</v>
       </c>
-      <c r="F16" s="20">
+      <c r="F18" s="20">
         <f>'TCS Data'!E4/'TCS Data'!E12</f>
         <v>1.6093640678478907</v>
       </c>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20">
+      <c r="G18" s="20"/>
+      <c r="H18" s="20">
         <f>'Infosys Data'!C4/'Infosys Data'!C12</f>
         <v>1.1779431121384314</v>
       </c>
-      <c r="I16" s="20">
+      <c r="I18" s="20">
         <f>'Infosys Data'!D4/'Infosys Data'!D12</f>
         <v>1.118739079790332</v>
       </c>
-      <c r="J16" s="20">
+      <c r="J18" s="20">
         <f>'Infosys Data'!E4/'Infosys Data'!E12</f>
         <v>1.1028113264995434</v>
       </c>
     </row>
-    <row r="17" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B17" s="15" t="s">
+    <row r="19" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B19" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="15"/>
-      <c r="D17" s="21">
+      <c r="C19" s="15"/>
+      <c r="D19" s="21">
         <f>'TCS Data'!C18/'TCS Data'!C4*360</f>
         <v>79.764035873643877</v>
       </c>
-      <c r="E17" s="21">
+      <c r="E19" s="21">
         <f>'TCS Data'!D18/'TCS Data'!D4*360</f>
         <v>80.067581872449594</v>
       </c>
-      <c r="F17" s="21">
+      <c r="F19" s="21">
         <f>'TCS Data'!E18/'TCS Data'!E4*360</f>
         <v>83.253278187714443</v>
       </c>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21">
+      <c r="G19" s="21"/>
+      <c r="H19" s="21">
         <f>'Infosys Data'!C18/'Infosys Data'!C4*360</f>
         <v>62.361702562565149</v>
       </c>
-      <c r="I17" s="21">
+      <c r="I19" s="21">
         <f>'Infosys Data'!D18/'Infosys Data'!D4*360</f>
         <v>70.732608837118505</v>
       </c>
-      <c r="J17" s="21">
+      <c r="J19" s="21">
         <f>'Infosys Data'!E18/'Infosys Data'!E4*360</f>
         <v>68.81943677526229</v>
       </c>
     </row>
-    <row r="18" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17"/>
-    </row>
-    <row r="19" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B19" s="14" t="s">
+    <row r="20" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+    </row>
+    <row r="21" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B21" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-    </row>
-    <row r="20" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B20" s="15" t="s">
+      <c r="C21" s="15"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+    </row>
+    <row r="22" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B22" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="15"/>
-      <c r="D20" s="20">
+      <c r="C22" s="15"/>
+      <c r="D22" s="20">
         <f>'TCS Data'!C14/'TCS Data'!C13</f>
         <v>8.5021675661328858E-2</v>
       </c>
-      <c r="E20" s="20">
+      <c r="E22" s="20">
         <f>'TCS Data'!D14/'TCS Data'!D13</f>
         <v>8.8640608250726602E-2</v>
       </c>
-      <c r="F20" s="20">
+      <c r="F22" s="20">
         <f>'TCS Data'!E14/'TCS Data'!E13</f>
         <v>9.9117733969352861E-2</v>
       </c>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20">
+      <c r="G22" s="20"/>
+      <c r="H22" s="20">
         <f>'Infosys Data'!C14/'Infosys Data'!C13</f>
         <v>0.11005609558794277</v>
       </c>
-      <c r="I20" s="20">
+      <c r="I22" s="20">
         <f>'Infosys Data'!D14/'Infosys Data'!D13</f>
         <v>9.4863588905533619E-2</v>
       </c>
-      <c r="J20" s="20">
+      <c r="J22" s="20">
         <f>'Infosys Data'!E14/'Infosys Data'!E13</f>
         <v>8.5860694232816379E-2</v>
       </c>
     </row>
-    <row r="21" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B21" s="15" t="s">
+    <row r="23" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B23" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="15"/>
-      <c r="D21" s="20">
+      <c r="C23" s="15"/>
+      <c r="D23" s="20">
         <f>'TCS Data'!C6/'TCS Data'!C9</f>
         <v>76.070603337612326</v>
       </c>
-      <c r="E21" s="20">
+      <c r="E23" s="20">
         <f>'TCS Data'!D6/'TCS Data'!D9</f>
         <v>82.642673521850895</v>
       </c>
-      <c r="F21" s="20">
+      <c r="F23" s="20">
         <f>'TCS Data'!E6/'TCS Data'!E9</f>
         <v>84.6821608040201</v>
       </c>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20">
+      <c r="G23" s="20"/>
+      <c r="H23" s="20">
         <f>'Infosys Data'!C6/'Infosys Data'!C9</f>
         <v>123.69718309859155</v>
       </c>
-      <c r="I21" s="20">
+      <c r="I23" s="20">
         <f>'Infosys Data'!D6/'Infosys Data'!D9</f>
         <v>77.5</v>
       </c>
-      <c r="J21" s="20">
+      <c r="J23" s="20">
         <f>'Infosys Data'!E6/'Infosys Data'!E9</f>
         <v>94.317307692307693</v>
       </c>
     </row>
-    <row r="27" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="M27" s="7"/>
-      <c r="N27" s="77"/>
-      <c r="O27" s="77"/>
-      <c r="P27" s="77"/>
-      <c r="Q27" s="77"/>
-      <c r="R27" s="77"/>
-      <c r="S27" s="77"/>
-    </row>
-    <row r="28" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="M28" s="7"/>
-      <c r="N28" s="7"/>
-      <c r="O28" s="7"/>
-      <c r="P28" s="7"/>
-      <c r="Q28" s="7"/>
-      <c r="R28" s="7"/>
-      <c r="S28" s="7"/>
-    </row>
     <row r="29" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="N29" s="8"/>
-      <c r="O29" s="8"/>
-      <c r="P29" s="8"/>
-      <c r="Q29" s="8"/>
-      <c r="R29" s="8"/>
-      <c r="S29" s="8"/>
+      <c r="M29" s="7"/>
+      <c r="N29" s="66"/>
+      <c r="O29" s="66"/>
+      <c r="P29" s="66"/>
+      <c r="Q29" s="66"/>
+      <c r="R29" s="66"/>
+      <c r="S29" s="66"/>
+    </row>
+    <row r="30" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="M30" s="7"/>
+      <c r="N30" s="7"/>
+      <c r="O30" s="7"/>
+      <c r="P30" s="7"/>
+      <c r="Q30" s="7"/>
+      <c r="R30" s="7"/>
+      <c r="S30" s="7"/>
+    </row>
+    <row r="31" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="N31" s="8"/>
+      <c r="O31" s="8"/>
+      <c r="P31" s="8"/>
+      <c r="Q31" s="8"/>
+      <c r="R31" s="8"/>
+      <c r="S31" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="N27:O27"/>
-    <mergeCell ref="P27:Q27"/>
-    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="N29:O29"/>
+    <mergeCell ref="P29:Q29"/>
+    <mergeCell ref="R29:S29"/>
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="H3:J3"/>
   </mergeCells>
@@ -10117,17 +10185,17 @@
       </c>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C3" s="80" t="s">
+      <c r="C3" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="81"/>
-      <c r="E3" s="82"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="71"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="80" t="s">
+      <c r="G3" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="83"/>
-      <c r="I3" s="82"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="71"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" s="37" t="s">
@@ -10241,17 +10309,17 @@
       <c r="I10" s="11"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C11" s="80" t="s">
+      <c r="C11" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="81"/>
-      <c r="E11" s="82"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="71"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="80" t="s">
+      <c r="G11" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="H11" s="81"/>
-      <c r="I11" s="82"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="71"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C12" s="37" t="s">
@@ -10356,17 +10424,17 @@
       <c r="I17" s="11"/>
     </row>
     <row r="18" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C18" s="80" t="s">
+      <c r="C18" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="81"/>
-      <c r="E18" s="82"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="71"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="80" t="s">
+      <c r="G18" s="69" t="s">
         <v>33</v>
       </c>
-      <c r="H18" s="81"/>
-      <c r="I18" s="82"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="71"/>
     </row>
     <row r="19" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C19" s="37" t="s">
@@ -10508,62 +10576,62 @@
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B3" s="75" t="s">
+      <c r="B3" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="67"/>
+      <c r="C3" s="74"/>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B4" s="76" t="s">
+      <c r="B4" s="83" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="67"/>
+      <c r="C4" s="74"/>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B5"/>
       <c r="C5"/>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B6" s="70" t="s">
+      <c r="B6" s="77" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="67"/>
+      <c r="C6" s="74"/>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B7" s="74" t="s">
+      <c r="B7" s="81" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="67"/>
+      <c r="C7" s="74"/>
     </row>
     <row r="8" spans="2:3" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="69" t="s">
+      <c r="B8" s="76" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="67"/>
+      <c r="C8" s="74"/>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B9" s="74" t="s">
+      <c r="B9" s="81" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="67"/>
+      <c r="C9" s="74"/>
     </row>
     <row r="10" spans="2:3" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="69" t="s">
+      <c r="B10" s="76" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="67"/>
+      <c r="C10" s="74"/>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B11"/>
       <c r="C11"/>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B12" s="70" t="s">
+      <c r="B12" s="77" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="67"/>
-    </row>
-    <row r="13" spans="2:3" ht="24" x14ac:dyDescent="0.3">
+      <c r="C12" s="74"/>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B13" s="22" t="s">
         <v>54</v>
       </c>
@@ -10615,12 +10683,12 @@
       <c r="C18"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B19" s="70" t="s">
+      <c r="B19" s="77" t="s">
         <v>56</v>
       </c>
-      <c r="C19" s="67"/>
-    </row>
-    <row r="20" spans="2:11" ht="24" x14ac:dyDescent="0.3">
+      <c r="C19" s="74"/>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="22" t="s">
         <v>54</v>
       </c>
@@ -10672,10 +10740,10 @@
       <c r="C24"/>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B25" s="70" t="s">
+      <c r="B25" s="77" t="s">
         <v>58</v>
       </c>
-      <c r="C25" s="67"/>
+      <c r="C25" s="74"/>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B26" s="22" t="s">
@@ -10706,88 +10774,88 @@
       <c r="C29" s="61"/>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B30" s="72" t="s">
+      <c r="B30" s="79" t="s">
         <v>79</v>
       </c>
       <c r="C30" s="61"/>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B31" s="72"/>
+      <c r="B31" s="79"/>
       <c r="C31" s="61"/>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B32" s="72"/>
+      <c r="B32" s="79"/>
       <c r="C32" s="61"/>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B33" s="72"/>
+      <c r="B33" s="79"/>
       <c r="C33" s="61"/>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B34" s="72"/>
+      <c r="B34" s="79"/>
       <c r="C34" s="61"/>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B35" s="72"/>
+      <c r="B35" s="79"/>
       <c r="C35" s="61"/>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B36" s="72"/>
+      <c r="B36" s="79"/>
       <c r="C36" s="61"/>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B37" s="72"/>
+      <c r="B37" s="79"/>
       <c r="C37" s="61"/>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B38" s="72"/>
+      <c r="B38" s="79"/>
       <c r="C38" s="61"/>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B39" s="72"/>
+      <c r="B39" s="79"/>
       <c r="C39" s="61"/>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B40" s="72"/>
+      <c r="B40" s="79"/>
       <c r="C40" s="61"/>
     </row>
     <row r="41" spans="2:3" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="72"/>
+      <c r="B41" s="79"/>
       <c r="C41" s="61"/>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B42" s="72"/>
+      <c r="B42" s="79"/>
       <c r="C42" s="61"/>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B43" s="72"/>
+      <c r="B43" s="79"/>
       <c r="C43" s="61"/>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B44" s="72"/>
+      <c r="B44" s="79"/>
       <c r="C44" s="61"/>
     </row>
     <row r="45" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="73"/>
+      <c r="B45" s="80"/>
       <c r="C45" s="61"/>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B46" s="71" t="s">
+      <c r="B46" s="78" t="s">
         <v>59</v>
       </c>
-      <c r="C46" s="67"/>
+      <c r="C46" s="74"/>
     </row>
     <row r="47" spans="2:3" ht="227.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="66" t="s">
+      <c r="B47" s="73" t="s">
         <v>78</v>
       </c>
-      <c r="C47" s="67"/>
+      <c r="C47" s="74"/>
     </row>
     <row r="48" spans="2:3" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="68" t="s">
+      <c r="B48" s="75" t="s">
         <v>60</v>
       </c>
-      <c r="C48" s="67"/>
+      <c r="C48" s="74"/>
     </row>
     <row r="54" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D54" s="24"/>
